--- a/Modèle Excel.xlsx
+++ b/Modèle Excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\2025 - Avignon\app_Avignon\app_Avignon_pdd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5CD35E-32E7-4F75-9263-B5C2A783CBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F4220E-C97A-4DE1-97ED-E1DC9B23C9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="2325" windowWidth="25185" windowHeight="12930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30660" yWindow="2475" windowWidth="25185" windowHeight="12930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Avignon 2025" sheetId="3" r:id="rId1"/>
@@ -97,13 +97,13 @@
     <t>Relâches</t>
   </si>
   <si>
-    <t>Validité</t>
-  </si>
-  <si>
     <t>[05-25]/07</t>
   </si>
   <si>
     <t>(14,18)/07</t>
+  </si>
+  <si>
+    <t>Séances</t>
   </si>
 </sst>
 </file>
@@ -750,7 +750,7 @@
         <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" t="s">
         <v>23</v>
@@ -782,7 +782,7 @@
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -808,7 +808,7 @@
         <v>17</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -831,7 +831,7 @@
         <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="2">
         <v>45858</v>
